--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937561</v>
+        <v>133937630</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1224,37 +1224,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595216</v>
+        <v>595406</v>
       </c>
       <c r="R7" t="n">
-        <v>7097632</v>
+        <v>7097841</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,64 +1308,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937628</v>
+        <v>133937561</v>
       </c>
       <c r="B8" t="n">
-        <v>91891</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595416</v>
+        <v>595216</v>
       </c>
       <c r="R8" t="n">
-        <v>7097833</v>
+        <v>7097632</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,7 +1390,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1404,7 +1400,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,44 +1415,48 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937630</v>
+        <v>133937628</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595406</v>
+        <v>595416</v>
       </c>
       <c r="R9" t="n">
-        <v>7097841</v>
+        <v>7097833</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2500,10 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937560</v>
+        <v>133937584</v>
       </c>
       <c r="B19" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,37 +2511,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595193</v>
+        <v>595175</v>
       </c>
       <c r="R19" t="n">
-        <v>7097655</v>
+        <v>7097596</v>
       </c>
       <c r="S19" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,16 +2593,6 @@
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2611,45 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937584</v>
+        <v>133937623</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>99162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595175</v>
+        <v>595221</v>
       </c>
       <c r="R20" t="n">
-        <v>7097596</v>
+        <v>7097668</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2681,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,53 +2694,59 @@
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937623</v>
+        <v>133937593</v>
       </c>
       <c r="B21" t="n">
-        <v>99162</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595221</v>
+        <v>595311</v>
       </c>
       <c r="R21" t="n">
-        <v>7097668</v>
+        <v>7097651</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2782,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2792,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,46 +2801,40 @@
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937593</v>
+        <v>133937589</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>80468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2854,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595311</v>
+        <v>595191</v>
       </c>
       <c r="R22" t="n">
-        <v>7097651</v>
+        <v>7097650</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2889,7 +2879,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2899,7 +2889,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,48 +2910,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937589</v>
+        <v>133937560</v>
       </c>
       <c r="B23" t="n">
-        <v>80468</v>
+        <v>80439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595191</v>
+        <v>595193</v>
       </c>
       <c r="R23" t="n">
-        <v>7097650</v>
+        <v>7097655</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2990,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +2990,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,6 +3003,16 @@
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133937567</v>
+        <v>133937566</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>91948</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,23 +3465,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3489,13 +3485,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595328</v>
+        <v>595306</v>
       </c>
       <c r="R28" t="n">
-        <v>7097836</v>
+        <v>7097799</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3524,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3534,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3565,10 +3561,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133937566</v>
+        <v>133937567</v>
       </c>
       <c r="B29" t="n">
-        <v>91948</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3576,19 +3572,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595306</v>
+        <v>595328</v>
       </c>
       <c r="R29" t="n">
-        <v>7097799</v>
+        <v>7097836</v>
       </c>
       <c r="S29" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4199,45 +4199,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133937595</v>
+        <v>133937627</v>
       </c>
       <c r="B35" t="n">
-        <v>79334</v>
+        <v>57145</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595379</v>
+        <v>595418</v>
       </c>
       <c r="R35" t="n">
-        <v>7097727</v>
+        <v>7097757</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4279,7 +4279,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4292,40 +4297,46 @@
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133937597</v>
+        <v>133937595</v>
       </c>
       <c r="B36" t="n">
-        <v>96358</v>
+        <v>79334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4335,10 +4346,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595445</v>
+        <v>595379</v>
       </c>
       <c r="R36" t="n">
-        <v>7097853</v>
+        <v>7097727</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4370,7 +4381,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4380,7 +4391,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4401,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133937627</v>
+        <v>133937597</v>
       </c>
       <c r="B37" t="n">
-        <v>57145</v>
+        <v>96358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4412,34 +4423,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595418</v>
+        <v>595445</v>
       </c>
       <c r="R37" t="n">
-        <v>7097757</v>
+        <v>7097853</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4471,7 +4482,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4481,12 +4492,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4499,17 +4505,11 @@
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5262,6 +5262,351 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133965737</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80439</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>29 maj, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>595190</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7097640</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>David Häggblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>David Häggblad, Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>133965736</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>29 maj, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>595176</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7097609</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>David Häggblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>David Häggblad, Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>133965739</v>
+      </c>
+      <c r="B47" t="n">
+        <v>83311</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>308</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>29 maj, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>595211</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7097663</v>
+      </c>
+      <c r="S47" t="n">
+        <v>8</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>David Häggblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>David Häggblad, Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -2282,48 +2282,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B17" t="n">
-        <v>80343</v>
+        <v>83319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R17" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,64 +2377,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B18" t="n">
-        <v>83319</v>
+        <v>80343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R18" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2463,7 +2459,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2473,7 +2469,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,15 +2484,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -2282,48 +2282,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B17" t="n">
-        <v>83319</v>
+        <v>80343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R17" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,60 +2377,64 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B18" t="n">
-        <v>80343</v>
+        <v>83319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R18" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,7 +2463,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2469,7 +2473,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,19 +2488,15 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -2282,48 +2282,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B17" t="n">
-        <v>80343</v>
+        <v>83319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R17" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,64 +2377,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B18" t="n">
-        <v>83319</v>
+        <v>80343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R18" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2463,7 +2459,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2473,7 +2469,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,22 +2484,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937584</v>
+        <v>133937560</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,37 +2511,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595175</v>
+        <v>595193</v>
       </c>
       <c r="R19" t="n">
-        <v>7097596</v>
+        <v>7097655</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,6 +2593,16 @@
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2601,45 +2611,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937623</v>
+        <v>133937584</v>
       </c>
       <c r="B20" t="n">
-        <v>99162</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595221</v>
+        <v>595175</v>
       </c>
       <c r="R20" t="n">
-        <v>7097668</v>
+        <v>7097596</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2671,7 +2681,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2691,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,59 +2704,53 @@
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937593</v>
+        <v>133937623</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>99162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595311</v>
+        <v>595221</v>
       </c>
       <c r="R21" t="n">
-        <v>7097651</v>
+        <v>7097668</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2778,7 +2782,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2792,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,40 +2805,46 @@
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937589</v>
+        <v>133937593</v>
       </c>
       <c r="B22" t="n">
-        <v>80468</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2844,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595191</v>
+        <v>595311</v>
       </c>
       <c r="R22" t="n">
-        <v>7097650</v>
+        <v>7097651</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2879,7 +2889,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2889,7 +2899,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,48 +2920,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937560</v>
+        <v>133937589</v>
       </c>
       <c r="B23" t="n">
-        <v>80439</v>
+        <v>80468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595193</v>
+        <v>595191</v>
       </c>
       <c r="R23" t="n">
-        <v>7097655</v>
+        <v>7097650</v>
       </c>
       <c r="S23" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2980,7 +2990,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2990,7 +3000,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3003,16 +3013,6 @@
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -2500,10 +2500,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937560</v>
+        <v>133937584</v>
       </c>
       <c r="B19" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,37 +2511,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595193</v>
+        <v>595175</v>
       </c>
       <c r="R19" t="n">
-        <v>7097655</v>
+        <v>7097596</v>
       </c>
       <c r="S19" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,16 +2593,6 @@
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2611,45 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937584</v>
+        <v>133937623</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>99162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595175</v>
+        <v>595221</v>
       </c>
       <c r="R20" t="n">
-        <v>7097596</v>
+        <v>7097668</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2681,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2691,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,53 +2694,59 @@
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937623</v>
+        <v>133937593</v>
       </c>
       <c r="B21" t="n">
-        <v>99162</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595221</v>
+        <v>595311</v>
       </c>
       <c r="R21" t="n">
-        <v>7097668</v>
+        <v>7097651</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2782,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2792,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,46 +2801,40 @@
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937593</v>
+        <v>133937589</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>80468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2854,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595311</v>
+        <v>595191</v>
       </c>
       <c r="R22" t="n">
-        <v>7097651</v>
+        <v>7097650</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2889,7 +2879,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2899,7 +2889,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,48 +2910,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937589</v>
+        <v>133937560</v>
       </c>
       <c r="B23" t="n">
-        <v>80468</v>
+        <v>80439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595191</v>
+        <v>595193</v>
       </c>
       <c r="R23" t="n">
-        <v>7097650</v>
+        <v>7097655</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2990,7 +2980,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3000,7 +2990,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,6 +3003,16 @@
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -3672,48 +3672,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133937569</v>
+        <v>133937592</v>
       </c>
       <c r="B30" t="n">
-        <v>96358</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595355</v>
+        <v>595271</v>
       </c>
       <c r="R30" t="n">
-        <v>7097870</v>
+        <v>7097671</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,16 +3765,6 @@
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -3783,30 +3773,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937573</v>
+        <v>133937569</v>
       </c>
       <c r="B31" t="n">
-        <v>91948</v>
+        <v>96358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3814,13 +3808,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595298</v>
+        <v>595355</v>
       </c>
       <c r="R31" t="n">
-        <v>7097915</v>
+        <v>7097870</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3849,7 +3843,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3859,7 +3853,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3890,10 +3884,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133937592</v>
+        <v>133937573</v>
       </c>
       <c r="B32" t="n">
-        <v>79334</v>
+        <v>91948</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,37 +3895,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595271</v>
+        <v>595298</v>
       </c>
       <c r="R32" t="n">
-        <v>7097671</v>
+        <v>7097915</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3960,7 +3950,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3970,7 +3960,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3983,6 +3973,16 @@
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133938031</v>
       </c>
       <c r="B2" t="n">
-        <v>80343</v>
+        <v>80357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -773,6 +773,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Patrik Eriksson</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -781,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133937572</v>
+        <v>133937574</v>
       </c>
       <c r="B3" t="n">
-        <v>91948</v>
+        <v>91943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,19 +802,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -812,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595308</v>
+        <v>595390</v>
       </c>
       <c r="R3" t="n">
-        <v>7097929</v>
+        <v>7097932</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -857,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133937574</v>
+        <v>133937572</v>
       </c>
       <c r="B4" t="n">
-        <v>91924</v>
+        <v>91967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,23 +913,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595390</v>
+        <v>595308</v>
       </c>
       <c r="R4" t="n">
-        <v>7097932</v>
+        <v>7097929</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -958,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -968,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1012,7 @@
         <v>133937626</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1119,7 @@
         <v>133937631</v>
       </c>
       <c r="B6" t="n">
-        <v>96358</v>
+        <v>96386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,32 +1223,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937630</v>
+        <v>133937628</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595406</v>
+        <v>595416</v>
       </c>
       <c r="R7" t="n">
-        <v>7097841</v>
+        <v>7097833</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1283,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937561</v>
+        <v>133937630</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,37 +1341,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595216</v>
+        <v>595406</v>
       </c>
       <c r="R8" t="n">
-        <v>7097632</v>
+        <v>7097841</v>
       </c>
       <c r="S8" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1400,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,64 +1425,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937628</v>
+        <v>133937561</v>
       </c>
       <c r="B9" t="n">
-        <v>91891</v>
+        <v>57962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595416</v>
+        <v>595216</v>
       </c>
       <c r="R9" t="n">
-        <v>7097833</v>
+        <v>7097632</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1511,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,22 +1532,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>133937633</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,7 +1663,7 @@
         <v>133937575</v>
       </c>
       <c r="B11" t="n">
-        <v>96358</v>
+        <v>96386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1774,7 @@
         <v>133937625</v>
       </c>
       <c r="B12" t="n">
-        <v>91924</v>
+        <v>91943</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1881,7 @@
         <v>133937599</v>
       </c>
       <c r="B13" t="n">
-        <v>96358</v>
+        <v>96386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,6 +1971,16 @@
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -1972,7 +1992,7 @@
         <v>133937596</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,6 +2082,16 @@
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2070,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133937564</v>
+        <v>133937585</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,17 +2131,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595317</v>
+        <v>595184</v>
       </c>
       <c r="R15" t="n">
-        <v>7097754</v>
+        <v>7097619</v>
       </c>
       <c r="S15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2150,7 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2165,12 +2195,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2181,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133937585</v>
+        <v>133937564</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,17 +2242,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595184</v>
+        <v>595317</v>
       </c>
       <c r="R16" t="n">
-        <v>7097619</v>
+        <v>7097754</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,7 +2281,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2261,7 +2291,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,6 +2304,16 @@
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2285,7 +2325,7 @@
         <v>133937634</v>
       </c>
       <c r="B17" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,7 +2432,7 @@
         <v>133937559</v>
       </c>
       <c r="B18" t="n">
-        <v>80343</v>
+        <v>80357</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,10 +2540,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937584</v>
+        <v>133937560</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>80453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2511,37 +2551,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595175</v>
+        <v>595193</v>
       </c>
       <c r="R19" t="n">
-        <v>7097596</v>
+        <v>7097655</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2570,7 +2610,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2580,7 +2620,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,6 +2633,16 @@
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2604,7 +2654,7 @@
         <v>133937623</v>
       </c>
       <c r="B20" t="n">
-        <v>99162</v>
+        <v>99190</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937593</v>
+        <v>133937584</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595311</v>
+        <v>595175</v>
       </c>
       <c r="R21" t="n">
-        <v>7097651</v>
+        <v>7097596</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2778,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2838,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2801,6 +2851,16 @@
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2812,7 +2872,7 @@
         <v>133937589</v>
       </c>
       <c r="B22" t="n">
-        <v>80468</v>
+        <v>80482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,6 +2962,16 @@
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -2910,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937560</v>
+        <v>133937593</v>
       </c>
       <c r="B23" t="n">
-        <v>80439</v>
+        <v>79348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2921,37 +2991,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595193</v>
+        <v>595311</v>
       </c>
       <c r="R23" t="n">
-        <v>7097655</v>
+        <v>7097651</v>
       </c>
       <c r="S23" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2980,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2990,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3005,12 +3075,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3021,48 +3091,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133937600</v>
+        <v>133937629</v>
       </c>
       <c r="B24" t="n">
-        <v>83311</v>
+        <v>96386</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595222</v>
+        <v>595437</v>
       </c>
       <c r="R24" t="n">
-        <v>7097669</v>
+        <v>7097860</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3091,7 +3161,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3171,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3114,56 +3184,62 @@
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133937629</v>
+        <v>133937600</v>
       </c>
       <c r="B25" t="n">
-        <v>96358</v>
+        <v>83325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595437</v>
+        <v>595222</v>
       </c>
       <c r="R25" t="n">
-        <v>7097860</v>
+        <v>7097669</v>
       </c>
       <c r="S25" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3192,7 +3268,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3202,7 +3278,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3217,22 +3293,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>133937591</v>
       </c>
       <c r="B26" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,6 +3402,16 @@
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -3333,7 +3423,7 @@
         <v>133937571</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3454,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133937566</v>
+        <v>133937567</v>
       </c>
       <c r="B28" t="n">
-        <v>91948</v>
+        <v>79348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,19 +3555,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3485,13 +3579,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595306</v>
+        <v>595328</v>
       </c>
       <c r="R28" t="n">
-        <v>7097799</v>
+        <v>7097836</v>
       </c>
       <c r="S28" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3520,7 +3614,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3530,7 +3624,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3561,10 +3655,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133937567</v>
+        <v>133937566</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>91967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3572,23 +3666,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3596,13 +3686,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595328</v>
+        <v>595306</v>
       </c>
       <c r="R29" t="n">
-        <v>7097836</v>
+        <v>7097799</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3631,7 +3721,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3641,7 +3731,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3675,7 +3765,7 @@
         <v>133937592</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,6 +3855,16 @@
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -3773,34 +3873,30 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937569</v>
+        <v>133937573</v>
       </c>
       <c r="B31" t="n">
-        <v>96358</v>
+        <v>91967</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3808,13 +3904,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595355</v>
+        <v>595298</v>
       </c>
       <c r="R31" t="n">
-        <v>7097870</v>
+        <v>7097915</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3843,7 +3939,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3853,7 +3949,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,30 +3980,34 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133937573</v>
+        <v>133937569</v>
       </c>
       <c r="B32" t="n">
-        <v>91948</v>
+        <v>96386</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3915,13 +4015,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595298</v>
+        <v>595355</v>
       </c>
       <c r="R32" t="n">
-        <v>7097915</v>
+        <v>7097870</v>
       </c>
       <c r="S32" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3950,7 +4050,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3960,7 +4060,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3991,10 +4091,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133937588</v>
+        <v>133937632</v>
       </c>
       <c r="B33" t="n">
-        <v>80439</v>
+        <v>83325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4002,37 +4102,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595190</v>
+        <v>595212</v>
       </c>
       <c r="R33" t="n">
-        <v>7097648</v>
+        <v>7097665</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4061,7 +4161,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4071,7 +4171,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4084,18 +4184,24 @@
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133937632</v>
+        <v>133937588</v>
       </c>
       <c r="B34" t="n">
-        <v>83311</v>
+        <v>80453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,37 +4209,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595212</v>
+        <v>595190</v>
       </c>
       <c r="R34" t="n">
-        <v>7097665</v>
+        <v>7097648</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,7 +4268,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4172,7 +4278,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4187,22 +4293,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>133937627</v>
       </c>
       <c r="B35" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,7 +4424,7 @@
         <v>133937595</v>
       </c>
       <c r="B36" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4404,6 +4514,16 @@
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -4415,7 +4535,7 @@
         <v>133937597</v>
       </c>
       <c r="B37" t="n">
-        <v>96358</v>
+        <v>96386</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4505,6 +4625,16 @@
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -4516,7 +4646,7 @@
         <v>133937563</v>
       </c>
       <c r="B38" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4635,7 +4765,7 @@
         <v>133937590</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,6 +4855,16 @@
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -4736,7 +4876,7 @@
         <v>133937621</v>
       </c>
       <c r="B40" t="n">
-        <v>80343</v>
+        <v>80357</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,7 +4983,7 @@
         <v>133937594</v>
       </c>
       <c r="B41" t="n">
-        <v>91924</v>
+        <v>91943</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4933,6 +5073,16 @@
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Brall</t>
+        </is>
+      </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -4944,7 +5094,7 @@
         <v>133937558</v>
       </c>
       <c r="B42" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5052,48 +5202,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133937570</v>
+        <v>133937586</v>
       </c>
       <c r="B43" t="n">
-        <v>91924</v>
+        <v>80357</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595369</v>
+        <v>595185</v>
       </c>
       <c r="R43" t="n">
-        <v>7097884</v>
+        <v>7097623</v>
       </c>
       <c r="S43" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5122,7 +5272,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5132,7 +5282,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5147,12 +5297,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5163,48 +5313,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133937586</v>
+        <v>133937570</v>
       </c>
       <c r="B44" t="n">
-        <v>80343</v>
+        <v>91943</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595185</v>
+        <v>595369</v>
       </c>
       <c r="R44" t="n">
-        <v>7097623</v>
+        <v>7097884</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5233,7 +5383,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5243,7 +5393,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5256,6 +5406,16 @@
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
@@ -5267,7 +5427,7 @@
         <v>133965737</v>
       </c>
       <c r="B45" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5382,7 +5542,7 @@
         <v>133965736</v>
       </c>
       <c r="B46" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5497,7 +5657,7 @@
         <v>133965739</v>
       </c>
       <c r="B47" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -1660,48 +1660,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133937575</v>
+        <v>133937625</v>
       </c>
       <c r="B11" t="n">
-        <v>96386</v>
+        <v>91943</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595436</v>
+        <v>595324</v>
       </c>
       <c r="R11" t="n">
-        <v>7097885</v>
+        <v>7097699</v>
       </c>
       <c r="S11" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,61 +1755,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133937625</v>
+        <v>133937599</v>
       </c>
       <c r="B12" t="n">
-        <v>91943</v>
+        <v>96386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595324</v>
+        <v>595445</v>
       </c>
       <c r="R12" t="n">
-        <v>7097699</v>
+        <v>7097892</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,44 +1862,48 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937599</v>
+        <v>133937596</v>
       </c>
       <c r="B13" t="n">
-        <v>96386</v>
+        <v>79348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595445</v>
+        <v>595406</v>
       </c>
       <c r="R13" t="n">
-        <v>7097892</v>
+        <v>7097778</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,48 +1989,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937596</v>
+        <v>133937575</v>
       </c>
       <c r="B14" t="n">
-        <v>79348</v>
+        <v>96386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595406</v>
+        <v>595436</v>
       </c>
       <c r="R14" t="n">
-        <v>7097778</v>
+        <v>7097885</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,12 +2084,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2540,48 +2540,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937560</v>
+        <v>133937623</v>
       </c>
       <c r="B19" t="n">
-        <v>80453</v>
+        <v>99190</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595193</v>
+        <v>595221</v>
       </c>
       <c r="R19" t="n">
-        <v>7097655</v>
+        <v>7097668</v>
       </c>
       <c r="S19" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,61 +2635,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937623</v>
+        <v>133937584</v>
       </c>
       <c r="B20" t="n">
-        <v>99190</v>
+        <v>79348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595221</v>
+        <v>595175</v>
       </c>
       <c r="R20" t="n">
-        <v>7097668</v>
+        <v>7097596</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2721,7 +2717,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2731,7 +2727,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2746,19 +2742,23 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937584</v>
+        <v>133937593</v>
       </c>
       <c r="B21" t="n">
         <v>79348</v>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595175</v>
+        <v>595311</v>
       </c>
       <c r="R21" t="n">
-        <v>7097596</v>
+        <v>7097651</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2980,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937593</v>
+        <v>133937560</v>
       </c>
       <c r="B23" t="n">
-        <v>79348</v>
+        <v>80453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595311</v>
+        <v>595193</v>
       </c>
       <c r="R23" t="n">
-        <v>7097651</v>
+        <v>7097655</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,12 +3075,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -4643,56 +4643,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133937563</v>
+        <v>133937621</v>
       </c>
       <c r="B38" t="n">
-        <v>57962</v>
+        <v>80357</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595342</v>
+        <v>595159</v>
       </c>
       <c r="R38" t="n">
-        <v>7097705</v>
+        <v>7097615</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4721,7 +4713,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4731,7 +4723,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4746,19 +4738,15 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4873,48 +4861,56 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133937621</v>
+        <v>133937563</v>
       </c>
       <c r="B40" t="n">
-        <v>80357</v>
+        <v>57962</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595159</v>
+        <v>595342</v>
       </c>
       <c r="R40" t="n">
-        <v>7097615</v>
+        <v>7097705</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4943,7 +4939,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4953,7 +4949,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4968,15 +4964,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133938031</v>
       </c>
       <c r="B2" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133937574</v>
+        <v>133937626</v>
       </c>
       <c r="B3" t="n">
-        <v>91943</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595390</v>
+        <v>595413</v>
       </c>
       <c r="R3" t="n">
-        <v>7097932</v>
+        <v>7097755</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,57 +886,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133937572</v>
+        <v>133937631</v>
       </c>
       <c r="B4" t="n">
-        <v>91967</v>
+        <v>96396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595308</v>
+        <v>595307</v>
       </c>
       <c r="R4" t="n">
-        <v>7097929</v>
+        <v>7097797</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,26 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133937626</v>
+        <v>133937574</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>91953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,34 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595413</v>
+        <v>595390</v>
       </c>
       <c r="R5" t="n">
-        <v>7097755</v>
+        <v>7097932</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,57 +1100,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133937631</v>
+        <v>133937572</v>
       </c>
       <c r="B6" t="n">
-        <v>96386</v>
+        <v>91977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595307</v>
+        <v>595308</v>
       </c>
       <c r="R6" t="n">
-        <v>7097797</v>
+        <v>7097929</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,60 +1207,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937628</v>
+        <v>133937561</v>
       </c>
       <c r="B7" t="n">
-        <v>91910</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595416</v>
+        <v>595216</v>
       </c>
       <c r="R7" t="n">
-        <v>7097833</v>
+        <v>7097632</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,44 +1318,48 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937630</v>
+        <v>133937628</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595406</v>
+        <v>595416</v>
       </c>
       <c r="R8" t="n">
-        <v>7097841</v>
+        <v>7097833</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937561</v>
+        <v>133937630</v>
       </c>
       <c r="B9" t="n">
-        <v>57962</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,37 +1452,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595216</v>
+        <v>595406</v>
       </c>
       <c r="R9" t="n">
-        <v>7097632</v>
+        <v>7097841</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,26 +1536,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>133937633</v>
       </c>
       <c r="B10" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,45 +1660,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133937625</v>
+        <v>133937599</v>
       </c>
       <c r="B11" t="n">
-        <v>91943</v>
+        <v>96396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595324</v>
+        <v>595445</v>
       </c>
       <c r="R11" t="n">
-        <v>7097699</v>
+        <v>7097892</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,44 +1755,48 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133937599</v>
+        <v>133937596</v>
       </c>
       <c r="B12" t="n">
-        <v>96386</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595445</v>
+        <v>595406</v>
       </c>
       <c r="R12" t="n">
-        <v>7097892</v>
+        <v>7097778</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1837,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,48 +1882,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937596</v>
+        <v>133937575</v>
       </c>
       <c r="B13" t="n">
-        <v>79348</v>
+        <v>96396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595406</v>
+        <v>595436</v>
       </c>
       <c r="R13" t="n">
-        <v>7097778</v>
+        <v>7097885</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1948,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,12 +1977,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1989,48 +1993,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937575</v>
+        <v>133937625</v>
       </c>
       <c r="B14" t="n">
-        <v>96386</v>
+        <v>91953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595436</v>
+        <v>595324</v>
       </c>
       <c r="R14" t="n">
-        <v>7097885</v>
+        <v>7097699</v>
       </c>
       <c r="S14" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2059,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,26 +2088,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>133937585</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>133937564</v>
       </c>
       <c r="B16" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>133937634</v>
       </c>
       <c r="B17" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>133937559</v>
       </c>
       <c r="B18" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,45 +2540,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937623</v>
+        <v>133937584</v>
       </c>
       <c r="B19" t="n">
-        <v>99190</v>
+        <v>79358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595221</v>
+        <v>595175</v>
       </c>
       <c r="R19" t="n">
-        <v>7097668</v>
+        <v>7097596</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,44 +2635,48 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937584</v>
+        <v>133937589</v>
       </c>
       <c r="B20" t="n">
-        <v>79348</v>
+        <v>80478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2682,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595175</v>
+        <v>595191</v>
       </c>
       <c r="R20" t="n">
-        <v>7097596</v>
+        <v>7097650</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2717,7 +2721,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2727,7 +2731,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2758,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937593</v>
+        <v>133937560</v>
       </c>
       <c r="B21" t="n">
-        <v>79348</v>
+        <v>80473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,37 +2773,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595311</v>
+        <v>595193</v>
       </c>
       <c r="R21" t="n">
-        <v>7097651</v>
+        <v>7097655</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2828,7 +2832,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,7 +2842,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,12 +2857,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2869,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937589</v>
+        <v>133937623</v>
       </c>
       <c r="B22" t="n">
-        <v>80482</v>
+        <v>99200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2880,34 +2884,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595191</v>
+        <v>595221</v>
       </c>
       <c r="R22" t="n">
-        <v>7097650</v>
+        <v>7097668</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2939,7 +2943,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2949,7 +2953,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,26 +2968,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937560</v>
+        <v>133937593</v>
       </c>
       <c r="B23" t="n">
-        <v>80453</v>
+        <v>79358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595193</v>
+        <v>595311</v>
       </c>
       <c r="R23" t="n">
-        <v>7097655</v>
+        <v>7097651</v>
       </c>
       <c r="S23" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,12 +3075,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3094,7 +3094,7 @@
         <v>133937629</v>
       </c>
       <c r="B24" t="n">
-        <v>96386</v>
+        <v>96396</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>133937600</v>
       </c>
       <c r="B25" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>133937591</v>
       </c>
       <c r="B26" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>133937571</v>
       </c>
       <c r="B27" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>133937567</v>
       </c>
       <c r="B28" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>133937566</v>
       </c>
       <c r="B29" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>133937592</v>
       </c>
       <c r="B30" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>133937573</v>
       </c>
       <c r="B31" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>133937569</v>
       </c>
       <c r="B32" t="n">
-        <v>96386</v>
+        <v>96396</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>133937632</v>
       </c>
       <c r="B33" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>133937588</v>
       </c>
       <c r="B34" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>133937627</v>
       </c>
       <c r="B35" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>133937595</v>
       </c>
       <c r="B36" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>133937597</v>
       </c>
       <c r="B37" t="n">
-        <v>96386</v>
+        <v>96396</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>133937621</v>
       </c>
       <c r="B38" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4750,10 +4750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133937590</v>
+        <v>133937563</v>
       </c>
       <c r="B39" t="n">
-        <v>79348</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,37 +4761,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595196</v>
+        <v>595342</v>
       </c>
       <c r="R39" t="n">
-        <v>7097666</v>
+        <v>7097705</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4820,7 +4828,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4830,7 +4838,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4845,12 +4853,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4861,10 +4869,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133937563</v>
+        <v>133937590</v>
       </c>
       <c r="B40" t="n">
-        <v>57962</v>
+        <v>79358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4872,45 +4880,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595342</v>
+        <v>595196</v>
       </c>
       <c r="R40" t="n">
-        <v>7097705</v>
+        <v>7097666</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4964,12 +4964,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4983,7 +4983,7 @@
         <v>133937594</v>
       </c>
       <c r="B41" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>133937558</v>
       </c>
       <c r="B42" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>133937586</v>
       </c>
       <c r="B43" t="n">
-        <v>80357</v>
+        <v>80367</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>133937570</v>
       </c>
       <c r="B44" t="n">
-        <v>91943</v>
+        <v>91953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>133965737</v>
       </c>
       <c r="B45" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>133965736</v>
       </c>
       <c r="B46" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>133965739</v>
       </c>
       <c r="B47" t="n">
-        <v>83325</v>
+        <v>83335</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -1223,48 +1223,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937561</v>
+        <v>133937628</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595216</v>
+        <v>595416</v>
       </c>
       <c r="R7" t="n">
-        <v>7097632</v>
+        <v>7097833</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,48 +1318,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937628</v>
+        <v>133937630</v>
       </c>
       <c r="B8" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595416</v>
+        <v>595406</v>
       </c>
       <c r="R8" t="n">
-        <v>7097833</v>
+        <v>7097841</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937630</v>
+        <v>133937561</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,37 +1448,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595406</v>
+        <v>595216</v>
       </c>
       <c r="R9" t="n">
-        <v>7097841</v>
+        <v>7097632</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,15 +1532,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1882,48 +1882,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937575</v>
+        <v>133937625</v>
       </c>
       <c r="B13" t="n">
-        <v>96396</v>
+        <v>91953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595436</v>
+        <v>595324</v>
       </c>
       <c r="R13" t="n">
-        <v>7097885</v>
+        <v>7097699</v>
       </c>
       <c r="S13" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,64 +1977,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937625</v>
+        <v>133937575</v>
       </c>
       <c r="B14" t="n">
-        <v>91953</v>
+        <v>96396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595324</v>
+        <v>595436</v>
       </c>
       <c r="R14" t="n">
-        <v>7097699</v>
+        <v>7097885</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,15 +2084,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2322,48 +2322,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B17" t="n">
-        <v>83343</v>
+        <v>80367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R17" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,60 +2417,64 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B18" t="n">
-        <v>80367</v>
+        <v>83343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R18" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,7 +2503,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2509,7 +2513,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,19 +2528,15 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2651,32 +2651,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937589</v>
+        <v>133937593</v>
       </c>
       <c r="B20" t="n">
-        <v>80478</v>
+        <v>79358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595191</v>
+        <v>595311</v>
       </c>
       <c r="R20" t="n">
-        <v>7097650</v>
+        <v>7097651</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,48 +2762,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937560</v>
+        <v>133937589</v>
       </c>
       <c r="B21" t="n">
-        <v>80473</v>
+        <v>80478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595193</v>
+        <v>595191</v>
       </c>
       <c r="R21" t="n">
-        <v>7097655</v>
+        <v>7097650</v>
       </c>
       <c r="S21" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,12 +2857,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2980,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937593</v>
+        <v>133937560</v>
       </c>
       <c r="B23" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595311</v>
+        <v>595193</v>
       </c>
       <c r="R23" t="n">
-        <v>7097651</v>
+        <v>7097655</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,12 +3075,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3091,48 +3091,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133937629</v>
+        <v>133937600</v>
       </c>
       <c r="B24" t="n">
-        <v>96396</v>
+        <v>83335</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595437</v>
+        <v>595222</v>
       </c>
       <c r="R24" t="n">
-        <v>7097860</v>
+        <v>7097669</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,22 +3186,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133937600</v>
+        <v>133937591</v>
       </c>
       <c r="B25" t="n">
-        <v>83335</v>
+        <v>79358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,21 +3213,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3233,13 +3237,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595222</v>
+        <v>595199</v>
       </c>
       <c r="R25" t="n">
-        <v>7097669</v>
+        <v>7097678</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3268,7 +3272,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3278,7 +3282,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3309,48 +3313,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133937591</v>
+        <v>133937629</v>
       </c>
       <c r="B26" t="n">
-        <v>79358</v>
+        <v>96396</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595199</v>
+        <v>595437</v>
       </c>
       <c r="R26" t="n">
-        <v>7097678</v>
+        <v>7097860</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3379,7 +3383,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3389,7 +3393,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,19 +3408,15 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4091,10 +4091,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133937632</v>
+        <v>133937588</v>
       </c>
       <c r="B33" t="n">
-        <v>83335</v>
+        <v>80473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,37 +4102,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595212</v>
+        <v>595190</v>
       </c>
       <c r="R33" t="n">
-        <v>7097665</v>
+        <v>7097648</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,22 +4186,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133937588</v>
+        <v>133937632</v>
       </c>
       <c r="B34" t="n">
-        <v>80473</v>
+        <v>83335</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,37 +4213,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595190</v>
+        <v>595212</v>
       </c>
       <c r="R34" t="n">
-        <v>7097648</v>
+        <v>7097665</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4268,7 +4272,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4278,7 +4282,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4293,19 +4297,15 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4750,10 +4750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133937563</v>
+        <v>133937590</v>
       </c>
       <c r="B39" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,45 +4761,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595342</v>
+        <v>595196</v>
       </c>
       <c r="R39" t="n">
-        <v>7097705</v>
+        <v>7097666</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4828,7 +4820,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4838,7 +4830,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4853,12 +4845,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4869,10 +4861,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133937590</v>
+        <v>133937563</v>
       </c>
       <c r="B40" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4880,37 +4872,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595196</v>
+        <v>595342</v>
       </c>
       <c r="R40" t="n">
-        <v>7097666</v>
+        <v>7097705</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4964,12 +4964,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133937626</v>
+        <v>133937574</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>91953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595413</v>
+        <v>595390</v>
       </c>
       <c r="R3" t="n">
-        <v>7097755</v>
+        <v>7097932</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,57 +886,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133937631</v>
+        <v>133937572</v>
       </c>
       <c r="B4" t="n">
-        <v>96396</v>
+        <v>91977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595307</v>
+        <v>595308</v>
       </c>
       <c r="R4" t="n">
-        <v>7097797</v>
+        <v>7097929</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,22 +993,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133937574</v>
+        <v>133937626</v>
       </c>
       <c r="B5" t="n">
-        <v>91953</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,34 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595390</v>
+        <v>595413</v>
       </c>
       <c r="R5" t="n">
-        <v>7097932</v>
+        <v>7097755</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1075,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,57 +1104,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133937572</v>
+        <v>133937631</v>
       </c>
       <c r="B6" t="n">
-        <v>91977</v>
+        <v>96396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595308</v>
+        <v>595307</v>
       </c>
       <c r="R6" t="n">
-        <v>7097929</v>
+        <v>7097797</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1182,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,64 +1211,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937628</v>
+        <v>133937561</v>
       </c>
       <c r="B7" t="n">
-        <v>91920</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595416</v>
+        <v>595216</v>
       </c>
       <c r="R7" t="n">
-        <v>7097833</v>
+        <v>7097632</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,44 +1318,48 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937630</v>
+        <v>133937628</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595406</v>
+        <v>595416</v>
       </c>
       <c r="R8" t="n">
-        <v>7097841</v>
+        <v>7097833</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937561</v>
+        <v>133937630</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,37 +1452,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595216</v>
+        <v>595406</v>
       </c>
       <c r="R9" t="n">
-        <v>7097632</v>
+        <v>7097841</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,19 +1536,15 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1882,48 +1882,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937625</v>
+        <v>133937575</v>
       </c>
       <c r="B13" t="n">
-        <v>91953</v>
+        <v>96396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595324</v>
+        <v>595436</v>
       </c>
       <c r="R13" t="n">
-        <v>7097699</v>
+        <v>7097885</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,60 +1977,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937575</v>
+        <v>133937625</v>
       </c>
       <c r="B14" t="n">
-        <v>96396</v>
+        <v>91953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595436</v>
+        <v>595324</v>
       </c>
       <c r="R14" t="n">
-        <v>7097885</v>
+        <v>7097699</v>
       </c>
       <c r="S14" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2059,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,23 +2088,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133937585</v>
+        <v>133937564</v>
       </c>
       <c r="B15" t="n">
         <v>79358</v>
@@ -2131,17 +2131,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595184</v>
+        <v>595317</v>
       </c>
       <c r="R15" t="n">
-        <v>7097619</v>
+        <v>7097754</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,12 +2195,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2211,7 +2211,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133937564</v>
+        <v>133937585</v>
       </c>
       <c r="B16" t="n">
         <v>79358</v>
@@ -2242,17 +2242,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595317</v>
+        <v>595184</v>
       </c>
       <c r="R16" t="n">
-        <v>7097754</v>
+        <v>7097619</v>
       </c>
       <c r="S16" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,12 +2306,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2540,10 +2540,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937584</v>
+        <v>133937560</v>
       </c>
       <c r="B19" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,37 +2551,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595175</v>
+        <v>595193</v>
       </c>
       <c r="R19" t="n">
-        <v>7097596</v>
+        <v>7097655</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,12 +2635,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2651,45 +2651,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937593</v>
+        <v>133937623</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>99200</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595311</v>
+        <v>595221</v>
       </c>
       <c r="R20" t="n">
-        <v>7097651</v>
+        <v>7097668</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2746,48 +2746,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937589</v>
+        <v>133937584</v>
       </c>
       <c r="B21" t="n">
-        <v>80478</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2797,10 +2793,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595191</v>
+        <v>595175</v>
       </c>
       <c r="R21" t="n">
-        <v>7097650</v>
+        <v>7097596</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2832,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2842,7 +2838,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,45 +2869,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937623</v>
+        <v>133937593</v>
       </c>
       <c r="B22" t="n">
-        <v>99200</v>
+        <v>79358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595221</v>
+        <v>595311</v>
       </c>
       <c r="R22" t="n">
-        <v>7097668</v>
+        <v>7097651</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2943,7 +2939,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2953,7 +2949,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,60 +2964,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937560</v>
+        <v>133937589</v>
       </c>
       <c r="B23" t="n">
-        <v>80473</v>
+        <v>80478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595193</v>
+        <v>595191</v>
       </c>
       <c r="R23" t="n">
-        <v>7097655</v>
+        <v>7097650</v>
       </c>
       <c r="S23" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,12 +3075,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3091,48 +3091,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133937600</v>
+        <v>133937629</v>
       </c>
       <c r="B24" t="n">
-        <v>83335</v>
+        <v>96396</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595222</v>
+        <v>595437</v>
       </c>
       <c r="R24" t="n">
-        <v>7097669</v>
+        <v>7097860</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,26 +3186,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133937591</v>
+        <v>133937600</v>
       </c>
       <c r="B25" t="n">
-        <v>79358</v>
+        <v>83335</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,21 +3209,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3237,13 +3233,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595199</v>
+        <v>595222</v>
       </c>
       <c r="R25" t="n">
-        <v>7097678</v>
+        <v>7097669</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,7 +3268,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3282,7 +3278,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,48 +3309,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133937629</v>
+        <v>133937591</v>
       </c>
       <c r="B26" t="n">
-        <v>96396</v>
+        <v>79358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595437</v>
+        <v>595199</v>
       </c>
       <c r="R26" t="n">
-        <v>7097860</v>
+        <v>7097678</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3383,7 +3379,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3393,7 +3389,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3408,15 +3404,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133937592</v>
+        <v>133937573</v>
       </c>
       <c r="B30" t="n">
-        <v>79358</v>
+        <v>91977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,37 +3773,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595271</v>
+        <v>595298</v>
       </c>
       <c r="R30" t="n">
-        <v>7097671</v>
+        <v>7097915</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3832,7 +3828,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3842,7 +3838,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3857,12 +3853,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3873,30 +3869,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937573</v>
+        <v>133937569</v>
       </c>
       <c r="B31" t="n">
-        <v>91977</v>
+        <v>96396</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595298</v>
+        <v>595355</v>
       </c>
       <c r="R31" t="n">
-        <v>7097915</v>
+        <v>7097870</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3980,48 +3980,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133937569</v>
+        <v>133937592</v>
       </c>
       <c r="B32" t="n">
-        <v>96396</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595355</v>
+        <v>595271</v>
       </c>
       <c r="R32" t="n">
-        <v>7097870</v>
+        <v>7097671</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,12 +4075,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4091,10 +4091,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133937588</v>
+        <v>133937632</v>
       </c>
       <c r="B33" t="n">
-        <v>80473</v>
+        <v>83335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,37 +4102,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595190</v>
+        <v>595212</v>
       </c>
       <c r="R33" t="n">
-        <v>7097648</v>
+        <v>7097665</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,26 +4186,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133937632</v>
+        <v>133937588</v>
       </c>
       <c r="B34" t="n">
-        <v>83335</v>
+        <v>80473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4213,37 +4209,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595212</v>
+        <v>595190</v>
       </c>
       <c r="R34" t="n">
-        <v>7097665</v>
+        <v>7097648</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4272,7 +4268,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4282,7 +4278,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4297,15 +4293,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4643,48 +4643,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133937621</v>
+        <v>133937563</v>
       </c>
       <c r="B38" t="n">
-        <v>80367</v>
+        <v>57972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595159</v>
+        <v>595342</v>
       </c>
       <c r="R38" t="n">
-        <v>7097615</v>
+        <v>7097705</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4713,7 +4721,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4723,7 +4731,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4738,60 +4746,64 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133937590</v>
+        <v>133937621</v>
       </c>
       <c r="B39" t="n">
-        <v>79358</v>
+        <v>80367</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595196</v>
+        <v>595159</v>
       </c>
       <c r="R39" t="n">
-        <v>7097666</v>
+        <v>7097615</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4820,7 +4832,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4830,7 +4842,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4845,26 +4857,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133937563</v>
+        <v>133937590</v>
       </c>
       <c r="B40" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4872,45 +4880,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595342</v>
+        <v>595196</v>
       </c>
       <c r="R40" t="n">
-        <v>7097705</v>
+        <v>7097666</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4964,12 +4964,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4980,10 +4980,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133937594</v>
+        <v>133937558</v>
       </c>
       <c r="B41" t="n">
-        <v>91953</v>
+        <v>79358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595325</v>
+        <v>595093</v>
       </c>
       <c r="R41" t="n">
-        <v>7097704</v>
+        <v>7097487</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5075,12 +5075,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5091,10 +5091,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133937558</v>
+        <v>133937594</v>
       </c>
       <c r="B42" t="n">
-        <v>79358</v>
+        <v>91953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5102,37 +5102,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595093</v>
+        <v>595325</v>
       </c>
       <c r="R42" t="n">
-        <v>7097487</v>
+        <v>7097704</v>
       </c>
       <c r="S42" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,12 +5186,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -1660,7 +1660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133937599</v>
+        <v>133937575</v>
       </c>
       <c r="B11" t="n">
         <v>96396</v>
@@ -1691,17 +1691,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595445</v>
+        <v>595436</v>
       </c>
       <c r="R11" t="n">
-        <v>7097892</v>
+        <v>7097885</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,12 +1755,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133937596</v>
+        <v>133937625</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>91953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,34 +1782,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595406</v>
+        <v>595324</v>
       </c>
       <c r="R12" t="n">
-        <v>7097778</v>
+        <v>7097699</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,23 +1866,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937575</v>
+        <v>133937599</v>
       </c>
       <c r="B13" t="n">
         <v>96396</v>
@@ -1913,17 +1909,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595436</v>
+        <v>595445</v>
       </c>
       <c r="R13" t="n">
-        <v>7097885</v>
+        <v>7097892</v>
       </c>
       <c r="S13" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,12 +1973,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1993,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937625</v>
+        <v>133937596</v>
       </c>
       <c r="B14" t="n">
-        <v>91953</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,34 +2000,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595324</v>
+        <v>595406</v>
       </c>
       <c r="R14" t="n">
-        <v>7097699</v>
+        <v>7097778</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,15 +2084,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2322,48 +2322,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B17" t="n">
-        <v>80367</v>
+        <v>83343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R17" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,64 +2417,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B18" t="n">
-        <v>83343</v>
+        <v>80367</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R18" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,7 +2499,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2513,7 +2509,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,15 +2524,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3091,48 +3091,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133937629</v>
+        <v>133937600</v>
       </c>
       <c r="B24" t="n">
-        <v>96396</v>
+        <v>83335</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595437</v>
+        <v>595222</v>
       </c>
       <c r="R24" t="n">
-        <v>7097860</v>
+        <v>7097669</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,22 +3186,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133937600</v>
+        <v>133937591</v>
       </c>
       <c r="B25" t="n">
-        <v>83335</v>
+        <v>79358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,21 +3213,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3233,13 +3237,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595222</v>
+        <v>595199</v>
       </c>
       <c r="R25" t="n">
-        <v>7097669</v>
+        <v>7097678</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3268,7 +3272,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3278,7 +3282,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3309,48 +3313,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133937591</v>
+        <v>133937629</v>
       </c>
       <c r="B26" t="n">
-        <v>79358</v>
+        <v>96396</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595199</v>
+        <v>595437</v>
       </c>
       <c r="R26" t="n">
-        <v>7097678</v>
+        <v>7097860</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3379,7 +3383,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3389,7 +3393,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,19 +3408,15 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -1223,48 +1223,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937561</v>
+        <v>133937628</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595216</v>
+        <v>595416</v>
       </c>
       <c r="R7" t="n">
-        <v>7097632</v>
+        <v>7097833</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,48 +1318,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937628</v>
+        <v>133937630</v>
       </c>
       <c r="B8" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595416</v>
+        <v>595406</v>
       </c>
       <c r="R8" t="n">
-        <v>7097833</v>
+        <v>7097841</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937630</v>
+        <v>133937561</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,37 +1448,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595406</v>
+        <v>595216</v>
       </c>
       <c r="R9" t="n">
-        <v>7097841</v>
+        <v>7097632</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,15 +1532,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,7 +1660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133937575</v>
+        <v>133937599</v>
       </c>
       <c r="B11" t="n">
         <v>96396</v>
@@ -1691,17 +1691,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595436</v>
+        <v>595445</v>
       </c>
       <c r="R11" t="n">
-        <v>7097885</v>
+        <v>7097892</v>
       </c>
       <c r="S11" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,12 +1755,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133937625</v>
+        <v>133937596</v>
       </c>
       <c r="B12" t="n">
-        <v>91953</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,34 +1782,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595324</v>
+        <v>595406</v>
       </c>
       <c r="R12" t="n">
-        <v>7097699</v>
+        <v>7097778</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,19 +1866,23 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937599</v>
+        <v>133937575</v>
       </c>
       <c r="B13" t="n">
         <v>96396</v>
@@ -1909,17 +1913,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595445</v>
+        <v>595436</v>
       </c>
       <c r="R13" t="n">
-        <v>7097892</v>
+        <v>7097885</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1948,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,12 +1977,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1989,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937596</v>
+        <v>133937625</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>91953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,34 +2004,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595406</v>
+        <v>595324</v>
       </c>
       <c r="R14" t="n">
-        <v>7097778</v>
+        <v>7097699</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2059,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,19 +2088,15 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2322,48 +2322,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B17" t="n">
-        <v>83343</v>
+        <v>80367</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R17" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,60 +2417,64 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B18" t="n">
-        <v>80367</v>
+        <v>83343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R18" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,7 +2503,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2509,7 +2513,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,19 +2528,15 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133937573</v>
+        <v>133937592</v>
       </c>
       <c r="B30" t="n">
-        <v>91977</v>
+        <v>79358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,33 +3773,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595298</v>
+        <v>595271</v>
       </c>
       <c r="R30" t="n">
-        <v>7097915</v>
+        <v>7097671</v>
       </c>
       <c r="S30" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3828,7 +3832,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3838,7 +3842,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,12 +3857,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3869,34 +3873,30 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937569</v>
+        <v>133937573</v>
       </c>
       <c r="B31" t="n">
-        <v>96396</v>
+        <v>91977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595355</v>
+        <v>595298</v>
       </c>
       <c r="R31" t="n">
-        <v>7097870</v>
+        <v>7097915</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3980,48 +3980,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133937592</v>
+        <v>133937569</v>
       </c>
       <c r="B32" t="n">
-        <v>79358</v>
+        <v>96396</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595271</v>
+        <v>595355</v>
       </c>
       <c r="R32" t="n">
-        <v>7097671</v>
+        <v>7097870</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,12 +4075,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -1223,48 +1223,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937628</v>
+        <v>133937561</v>
       </c>
       <c r="B7" t="n">
-        <v>91920</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595416</v>
+        <v>595216</v>
       </c>
       <c r="R7" t="n">
-        <v>7097833</v>
+        <v>7097632</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,44 +1318,48 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937630</v>
+        <v>133937628</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595406</v>
+        <v>595416</v>
       </c>
       <c r="R8" t="n">
-        <v>7097841</v>
+        <v>7097833</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937561</v>
+        <v>133937630</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,37 +1452,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595216</v>
+        <v>595406</v>
       </c>
       <c r="R9" t="n">
-        <v>7097632</v>
+        <v>7097841</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,19 +1536,15 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133937592</v>
+        <v>133937573</v>
       </c>
       <c r="B30" t="n">
-        <v>79358</v>
+        <v>91977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,37 +3773,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595271</v>
+        <v>595298</v>
       </c>
       <c r="R30" t="n">
-        <v>7097671</v>
+        <v>7097915</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3832,7 +3828,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3842,7 +3838,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3857,12 +3853,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3873,30 +3869,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937573</v>
+        <v>133937569</v>
       </c>
       <c r="B31" t="n">
-        <v>91977</v>
+        <v>96396</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595298</v>
+        <v>595355</v>
       </c>
       <c r="R31" t="n">
-        <v>7097915</v>
+        <v>7097870</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3980,48 +3980,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133937569</v>
+        <v>133937592</v>
       </c>
       <c r="B32" t="n">
-        <v>96396</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595355</v>
+        <v>595271</v>
       </c>
       <c r="R32" t="n">
-        <v>7097870</v>
+        <v>7097671</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,12 +4075,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133938031</v>
       </c>
       <c r="B2" t="n">
-        <v>80367</v>
+        <v>80368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>133937574</v>
       </c>
       <c r="B3" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>133937572</v>
       </c>
       <c r="B4" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>133937631</v>
       </c>
       <c r="B6" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>133937628</v>
       </c>
       <c r="B8" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>133937630</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>133937633</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133937599</v>
+        <v>133937575</v>
       </c>
       <c r="B11" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,17 +1691,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595445</v>
+        <v>595436</v>
       </c>
       <c r="R11" t="n">
-        <v>7097892</v>
+        <v>7097885</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,12 +1755,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133937596</v>
+        <v>133937625</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>91955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,34 +1782,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595406</v>
+        <v>595324</v>
       </c>
       <c r="R12" t="n">
-        <v>7097778</v>
+        <v>7097699</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,26 +1866,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937575</v>
+        <v>133937599</v>
       </c>
       <c r="B13" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,17 +1909,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595436</v>
+        <v>595445</v>
       </c>
       <c r="R13" t="n">
-        <v>7097885</v>
+        <v>7097892</v>
       </c>
       <c r="S13" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1948,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1958,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,12 +1973,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1993,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937625</v>
+        <v>133937596</v>
       </c>
       <c r="B14" t="n">
-        <v>91953</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,34 +2000,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595324</v>
+        <v>595406</v>
       </c>
       <c r="R14" t="n">
-        <v>7097699</v>
+        <v>7097778</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,22 +2084,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133937564</v>
+        <v>133937585</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,17 +2131,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595317</v>
+        <v>595184</v>
       </c>
       <c r="R15" t="n">
-        <v>7097754</v>
+        <v>7097619</v>
       </c>
       <c r="S15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,12 +2195,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2211,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133937585</v>
+        <v>133937564</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2242,17 +2242,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595184</v>
+        <v>595317</v>
       </c>
       <c r="R16" t="n">
-        <v>7097619</v>
+        <v>7097754</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,12 +2306,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2325,7 +2325,7 @@
         <v>133937559</v>
       </c>
       <c r="B17" t="n">
-        <v>80367</v>
+        <v>80368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>133937634</v>
       </c>
       <c r="B18" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,48 +2540,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937560</v>
+        <v>133937589</v>
       </c>
       <c r="B19" t="n">
-        <v>80473</v>
+        <v>80479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595193</v>
+        <v>595191</v>
       </c>
       <c r="R19" t="n">
-        <v>7097655</v>
+        <v>7097650</v>
       </c>
       <c r="S19" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,12 +2635,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2651,48 +2651,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937623</v>
+        <v>133937560</v>
       </c>
       <c r="B20" t="n">
-        <v>99200</v>
+        <v>80474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595221</v>
+        <v>595193</v>
       </c>
       <c r="R20" t="n">
-        <v>7097668</v>
+        <v>7097655</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2746,57 +2746,61 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937584</v>
+        <v>133937623</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>99202</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595175</v>
+        <v>595221</v>
       </c>
       <c r="R21" t="n">
-        <v>7097596</v>
+        <v>7097668</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2828,7 +2832,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,7 +2842,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,26 +2857,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937593</v>
+        <v>133937584</v>
       </c>
       <c r="B22" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595311</v>
+        <v>595175</v>
       </c>
       <c r="R22" t="n">
-        <v>7097651</v>
+        <v>7097596</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,32 +2980,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937589</v>
+        <v>133937593</v>
       </c>
       <c r="B23" t="n">
-        <v>80478</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595191</v>
+        <v>595311</v>
       </c>
       <c r="R23" t="n">
-        <v>7097650</v>
+        <v>7097651</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3094,7 +3094,7 @@
         <v>133937600</v>
       </c>
       <c r="B24" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>133937591</v>
       </c>
       <c r="B25" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>133937629</v>
       </c>
       <c r="B26" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>133937567</v>
       </c>
       <c r="B28" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>133937566</v>
       </c>
       <c r="B29" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133937573</v>
+        <v>133937592</v>
       </c>
       <c r="B30" t="n">
-        <v>91977</v>
+        <v>79359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3773,33 +3773,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595298</v>
+        <v>595271</v>
       </c>
       <c r="R30" t="n">
-        <v>7097915</v>
+        <v>7097671</v>
       </c>
       <c r="S30" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3828,7 +3832,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3838,7 +3842,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,12 +3857,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3869,34 +3873,30 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937569</v>
+        <v>133937573</v>
       </c>
       <c r="B31" t="n">
-        <v>96396</v>
+        <v>91979</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595355</v>
+        <v>595298</v>
       </c>
       <c r="R31" t="n">
-        <v>7097870</v>
+        <v>7097915</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3980,48 +3980,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133937592</v>
+        <v>133937569</v>
       </c>
       <c r="B32" t="n">
-        <v>79358</v>
+        <v>96398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595271</v>
+        <v>595355</v>
       </c>
       <c r="R32" t="n">
-        <v>7097671</v>
+        <v>7097870</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,12 +4075,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4094,7 +4094,7 @@
         <v>133937632</v>
       </c>
       <c r="B33" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>133937588</v>
       </c>
       <c r="B34" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>133937595</v>
       </c>
       <c r="B36" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>133937597</v>
       </c>
       <c r="B37" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>133937621</v>
       </c>
       <c r="B39" t="n">
-        <v>80367</v>
+        <v>80368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>133937590</v>
       </c>
       <c r="B40" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>133937558</v>
       </c>
       <c r="B41" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>133937594</v>
       </c>
       <c r="B42" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>133937586</v>
       </c>
       <c r="B43" t="n">
-        <v>80367</v>
+        <v>80368</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>133937570</v>
       </c>
       <c r="B44" t="n">
-        <v>91953</v>
+        <v>91955</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>133965737</v>
       </c>
       <c r="B45" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>133965736</v>
       </c>
       <c r="B46" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>133965739</v>
       </c>
       <c r="B47" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133937574</v>
+        <v>133937626</v>
       </c>
       <c r="B3" t="n">
-        <v>91955</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595390</v>
+        <v>595413</v>
       </c>
       <c r="R3" t="n">
-        <v>7097932</v>
+        <v>7097755</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,57 +886,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133937572</v>
+        <v>133937631</v>
       </c>
       <c r="B4" t="n">
-        <v>91979</v>
+        <v>96398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595308</v>
+        <v>595307</v>
       </c>
       <c r="R4" t="n">
-        <v>7097929</v>
+        <v>7097797</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,26 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133937626</v>
+        <v>133937574</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>91955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,34 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595413</v>
+        <v>595390</v>
       </c>
       <c r="R5" t="n">
-        <v>7097755</v>
+        <v>7097932</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,57 +1100,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133937631</v>
+        <v>133937572</v>
       </c>
       <c r="B6" t="n">
-        <v>96398</v>
+        <v>91979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595307</v>
+        <v>595308</v>
       </c>
       <c r="R6" t="n">
-        <v>7097797</v>
+        <v>7097929</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,15 +1207,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1660,7 +1660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133937575</v>
+        <v>133937599</v>
       </c>
       <c r="B11" t="n">
         <v>96398</v>
@@ -1691,17 +1691,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595436</v>
+        <v>595445</v>
       </c>
       <c r="R11" t="n">
-        <v>7097885</v>
+        <v>7097892</v>
       </c>
       <c r="S11" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,12 +1755,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133937625</v>
+        <v>133937596</v>
       </c>
       <c r="B12" t="n">
-        <v>91955</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,34 +1782,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595324</v>
+        <v>595406</v>
       </c>
       <c r="R12" t="n">
-        <v>7097699</v>
+        <v>7097778</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,57 +1866,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937599</v>
+        <v>133937625</v>
       </c>
       <c r="B13" t="n">
-        <v>96398</v>
+        <v>91955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595445</v>
+        <v>595324</v>
       </c>
       <c r="R13" t="n">
-        <v>7097892</v>
+        <v>7097699</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1948,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,64 +1977,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937596</v>
+        <v>133937575</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>96398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595406</v>
+        <v>595436</v>
       </c>
       <c r="R14" t="n">
-        <v>7097778</v>
+        <v>7097885</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,12 +2084,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2322,48 +2322,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B17" t="n">
-        <v>80368</v>
+        <v>83344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R17" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,64 +2417,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B18" t="n">
-        <v>83344</v>
+        <v>80368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R18" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,7 +2499,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2513,7 +2509,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,22 +2524,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937589</v>
+        <v>133937623</v>
       </c>
       <c r="B19" t="n">
-        <v>80479</v>
+        <v>99202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,34 +2551,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595191</v>
+        <v>595221</v>
       </c>
       <c r="R19" t="n">
-        <v>7097650</v>
+        <v>7097668</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,26 +2635,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937560</v>
+        <v>133937584</v>
       </c>
       <c r="B20" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,37 +2658,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595193</v>
+        <v>595175</v>
       </c>
       <c r="R20" t="n">
-        <v>7097655</v>
+        <v>7097596</v>
       </c>
       <c r="S20" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2721,7 +2717,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2731,7 +2727,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2746,12 +2742,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2762,45 +2758,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937623</v>
+        <v>133937593</v>
       </c>
       <c r="B21" t="n">
-        <v>99202</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595221</v>
+        <v>595311</v>
       </c>
       <c r="R21" t="n">
-        <v>7097668</v>
+        <v>7097651</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2832,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2842,7 +2838,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,44 +2853,48 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937584</v>
+        <v>133937589</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>80479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595175</v>
+        <v>595191</v>
       </c>
       <c r="R22" t="n">
-        <v>7097596</v>
+        <v>7097650</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937593</v>
+        <v>133937560</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595311</v>
+        <v>595193</v>
       </c>
       <c r="R23" t="n">
-        <v>7097651</v>
+        <v>7097655</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,12 +3075,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3091,48 +3091,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133937600</v>
+        <v>133937629</v>
       </c>
       <c r="B24" t="n">
-        <v>83336</v>
+        <v>96398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595222</v>
+        <v>595437</v>
       </c>
       <c r="R24" t="n">
-        <v>7097669</v>
+        <v>7097860</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3186,26 +3186,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133937591</v>
+        <v>133937600</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>83336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,21 +3209,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3237,13 +3233,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595199</v>
+        <v>595222</v>
       </c>
       <c r="R25" t="n">
-        <v>7097678</v>
+        <v>7097669</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,7 +3268,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3282,7 +3278,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,48 +3309,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133937629</v>
+        <v>133937591</v>
       </c>
       <c r="B26" t="n">
-        <v>96398</v>
+        <v>79359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595437</v>
+        <v>595199</v>
       </c>
       <c r="R26" t="n">
-        <v>7097860</v>
+        <v>7097678</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3383,7 +3379,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3393,7 +3389,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3408,15 +3404,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4309,45 +4309,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133937627</v>
+        <v>133937595</v>
       </c>
       <c r="B35" t="n">
-        <v>57162</v>
+        <v>79359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595418</v>
+        <v>595379</v>
       </c>
       <c r="R35" t="n">
-        <v>7097757</v>
+        <v>7097727</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4389,12 +4389,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4409,44 +4404,48 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133937595</v>
+        <v>133937597</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>96398</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4456,10 +4455,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595379</v>
+        <v>595445</v>
       </c>
       <c r="R36" t="n">
-        <v>7097727</v>
+        <v>7097853</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4491,7 +4490,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4501,7 +4500,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4532,10 +4531,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133937597</v>
+        <v>133937627</v>
       </c>
       <c r="B37" t="n">
-        <v>96398</v>
+        <v>57162</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,34 +4542,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2809</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595445</v>
+        <v>595418</v>
       </c>
       <c r="R37" t="n">
-        <v>7097853</v>
+        <v>7097757</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4602,7 +4601,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4612,7 +4611,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4627,19 +4631,15 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4980,10 +4980,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133937558</v>
+        <v>133937594</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>91955</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595093</v>
+        <v>595325</v>
       </c>
       <c r="R41" t="n">
-        <v>7097487</v>
+        <v>7097704</v>
       </c>
       <c r="S41" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5075,12 +5075,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5091,10 +5091,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133937594</v>
+        <v>133937558</v>
       </c>
       <c r="B42" t="n">
-        <v>91955</v>
+        <v>79359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5102,37 +5102,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595325</v>
+        <v>595093</v>
       </c>
       <c r="R42" t="n">
-        <v>7097704</v>
+        <v>7097487</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,12 +5186,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -791,45 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133937631</v>
+        <v>133937574</v>
       </c>
       <c r="B3" t="n">
-        <v>96399</v>
+        <v>91956</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595307</v>
+        <v>595390</v>
       </c>
       <c r="R3" t="n">
-        <v>7097797</v>
+        <v>7097932</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,15 +886,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133937574</v>
+        <v>133937572</v>
       </c>
       <c r="B5" t="n">
-        <v>91956</v>
+        <v>91980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,23 +1020,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595390</v>
+        <v>595308</v>
       </c>
       <c r="R5" t="n">
-        <v>7097932</v>
+        <v>7097929</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,41 +1116,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133937572</v>
+        <v>133937631</v>
       </c>
       <c r="B6" t="n">
-        <v>91980</v>
+        <v>96399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595308</v>
+        <v>595307</v>
       </c>
       <c r="R6" t="n">
-        <v>7097929</v>
+        <v>7097797</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1182,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,48 +1211,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937630</v>
+        <v>133937628</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595406</v>
+        <v>595416</v>
       </c>
       <c r="R7" t="n">
-        <v>7097841</v>
+        <v>7097833</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,48 +1330,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937628</v>
+        <v>133937561</v>
       </c>
       <c r="B8" t="n">
-        <v>91923</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595416</v>
+        <v>595216</v>
       </c>
       <c r="R8" t="n">
-        <v>7097833</v>
+        <v>7097632</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,22 +1425,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937561</v>
+        <v>133937630</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,37 +1452,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595216</v>
+        <v>595406</v>
       </c>
       <c r="R9" t="n">
-        <v>7097632</v>
+        <v>7097841</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,19 +1536,15 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,7 +1660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133937599</v>
+        <v>133937575</v>
       </c>
       <c r="B11" t="n">
         <v>96399</v>
@@ -1691,17 +1691,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595445</v>
+        <v>595436</v>
       </c>
       <c r="R11" t="n">
-        <v>7097892</v>
+        <v>7097885</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,12 +1755,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1771,32 +1771,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133937596</v>
+        <v>133937599</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>96399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595406</v>
+        <v>595445</v>
       </c>
       <c r="R12" t="n">
-        <v>7097778</v>
+        <v>7097892</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,48 +1989,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937575</v>
+        <v>133937596</v>
       </c>
       <c r="B14" t="n">
-        <v>96399</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595436</v>
+        <v>595406</v>
       </c>
       <c r="R14" t="n">
-        <v>7097885</v>
+        <v>7097778</v>
       </c>
       <c r="S14" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,12 +2084,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2322,48 +2322,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B17" t="n">
-        <v>83344</v>
+        <v>80368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R17" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,60 +2417,64 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B18" t="n">
-        <v>80368</v>
+        <v>83344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R18" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,7 +2503,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2509,7 +2513,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,19 +2528,15 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2762,48 +2762,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937623</v>
+        <v>133937560</v>
       </c>
       <c r="B21" t="n">
-        <v>99203</v>
+        <v>80474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595221</v>
+        <v>595193</v>
       </c>
       <c r="R21" t="n">
-        <v>7097668</v>
+        <v>7097655</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,15 +2857,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2980,48 +2984,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937560</v>
+        <v>133937623</v>
       </c>
       <c r="B23" t="n">
-        <v>80474</v>
+        <v>99203</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595193</v>
+        <v>595221</v>
       </c>
       <c r="R23" t="n">
-        <v>7097655</v>
+        <v>7097668</v>
       </c>
       <c r="S23" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,7 +3054,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3060,7 +3064,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,19 +3079,15 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,48 +3202,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133937591</v>
+        <v>133937629</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>96399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595199</v>
+        <v>595437</v>
       </c>
       <c r="R25" t="n">
-        <v>7097678</v>
+        <v>7097860</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3297,64 +3297,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133937629</v>
+        <v>133937591</v>
       </c>
       <c r="B26" t="n">
-        <v>96399</v>
+        <v>79359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595437</v>
+        <v>595199</v>
       </c>
       <c r="R26" t="n">
-        <v>7097860</v>
+        <v>7097678</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3383,7 +3379,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3393,7 +3389,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3408,15 +3404,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3762,30 +3762,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133937573</v>
+        <v>133937569</v>
       </c>
       <c r="B30" t="n">
-        <v>91980</v>
+        <v>96399</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3793,13 +3797,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595298</v>
+        <v>595355</v>
       </c>
       <c r="R30" t="n">
-        <v>7097915</v>
+        <v>7097870</v>
       </c>
       <c r="S30" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3828,7 +3832,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3838,7 +3842,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3869,34 +3873,30 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937569</v>
+        <v>133937573</v>
       </c>
       <c r="B31" t="n">
-        <v>96399</v>
+        <v>91980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595355</v>
+        <v>595298</v>
       </c>
       <c r="R31" t="n">
-        <v>7097870</v>
+        <v>7097915</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4309,45 +4309,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133937595</v>
+        <v>133937627</v>
       </c>
       <c r="B35" t="n">
-        <v>79359</v>
+        <v>57162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595379</v>
+        <v>595418</v>
       </c>
       <c r="R35" t="n">
-        <v>7097727</v>
+        <v>7097757</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4389,7 +4389,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4404,48 +4409,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133937597</v>
+        <v>133937595</v>
       </c>
       <c r="B36" t="n">
-        <v>96399</v>
+        <v>79359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4455,10 +4456,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595445</v>
+        <v>595379</v>
       </c>
       <c r="R36" t="n">
-        <v>7097853</v>
+        <v>7097727</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4490,7 +4491,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4500,7 +4501,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4531,10 +4532,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133937627</v>
+        <v>133937597</v>
       </c>
       <c r="B37" t="n">
-        <v>57162</v>
+        <v>96399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4542,34 +4543,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595418</v>
+        <v>595445</v>
       </c>
       <c r="R37" t="n">
-        <v>7097757</v>
+        <v>7097853</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4601,7 +4602,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4611,12 +4612,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4631,22 +4627,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133937563</v>
+        <v>133937590</v>
       </c>
       <c r="B38" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4654,45 +4654,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595342</v>
+        <v>595196</v>
       </c>
       <c r="R38" t="n">
-        <v>7097705</v>
+        <v>7097666</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4721,7 +4713,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4731,7 +4723,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4746,12 +4738,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4762,48 +4754,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133937590</v>
+        <v>133937621</v>
       </c>
       <c r="B39" t="n">
-        <v>79359</v>
+        <v>80368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595196</v>
+        <v>595159</v>
       </c>
       <c r="R39" t="n">
-        <v>7097666</v>
+        <v>7097615</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4832,7 +4824,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4842,7 +4834,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4857,64 +4849,68 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133937621</v>
+        <v>133937563</v>
       </c>
       <c r="B40" t="n">
-        <v>80368</v>
+        <v>57972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595159</v>
+        <v>595342</v>
       </c>
       <c r="R40" t="n">
-        <v>7097615</v>
+        <v>7097705</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4943,7 +4939,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4953,7 +4949,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4968,15 +4964,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5202,48 +5202,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133937586</v>
+        <v>133937570</v>
       </c>
       <c r="B43" t="n">
-        <v>80368</v>
+        <v>91956</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595185</v>
+        <v>595369</v>
       </c>
       <c r="R43" t="n">
-        <v>7097623</v>
+        <v>7097884</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5297,12 +5297,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5313,48 +5313,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133937570</v>
+        <v>133937586</v>
       </c>
       <c r="B44" t="n">
-        <v>91956</v>
+        <v>80368</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595369</v>
+        <v>595185</v>
       </c>
       <c r="R44" t="n">
-        <v>7097884</v>
+        <v>7097623</v>
       </c>
       <c r="S44" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5408,12 +5408,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133938031</v>
       </c>
       <c r="B2" t="n">
-        <v>80368</v>
+        <v>80375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133937574</v>
+        <v>133937626</v>
       </c>
       <c r="B3" t="n">
-        <v>91956</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595390</v>
+        <v>595413</v>
       </c>
       <c r="R3" t="n">
-        <v>7097932</v>
+        <v>7097755</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,48 +886,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133937626</v>
+        <v>133937631</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>96406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595413</v>
+        <v>595307</v>
       </c>
       <c r="R4" t="n">
-        <v>7097755</v>
+        <v>7097797</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133937572</v>
+        <v>133937574</v>
       </c>
       <c r="B5" t="n">
-        <v>91980</v>
+        <v>91963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,19 +1016,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595308</v>
+        <v>595390</v>
       </c>
       <c r="R5" t="n">
-        <v>7097929</v>
+        <v>7097932</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,45 +1116,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133937631</v>
+        <v>133937572</v>
       </c>
       <c r="B6" t="n">
-        <v>96399</v>
+        <v>91987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595307</v>
+        <v>595308</v>
       </c>
       <c r="R6" t="n">
-        <v>7097797</v>
+        <v>7097929</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,60 +1207,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937628</v>
+        <v>133937561</v>
       </c>
       <c r="B7" t="n">
-        <v>91923</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595416</v>
+        <v>595216</v>
       </c>
       <c r="R7" t="n">
-        <v>7097833</v>
+        <v>7097632</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,60 +1318,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937561</v>
+        <v>133937628</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595216</v>
+        <v>595416</v>
       </c>
       <c r="R8" t="n">
-        <v>7097632</v>
+        <v>7097833</v>
       </c>
       <c r="S8" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1410,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,26 +1429,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>133937630</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>133937633</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>133937575</v>
       </c>
       <c r="B11" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>133937599</v>
       </c>
       <c r="B12" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937625</v>
+        <v>133937596</v>
       </c>
       <c r="B13" t="n">
-        <v>91956</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,34 +1893,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595324</v>
+        <v>595406</v>
       </c>
       <c r="R13" t="n">
-        <v>7097699</v>
+        <v>7097778</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,22 +1977,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937596</v>
+        <v>133937625</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>91963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,34 +2004,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595406</v>
+        <v>595324</v>
       </c>
       <c r="R14" t="n">
-        <v>7097778</v>
+        <v>7097699</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2059,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,26 +2088,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133937585</v>
+        <v>133937564</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,17 +2131,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595184</v>
+        <v>595317</v>
       </c>
       <c r="R15" t="n">
-        <v>7097619</v>
+        <v>7097754</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,12 +2195,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2211,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133937564</v>
+        <v>133937585</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2242,17 +2242,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595317</v>
+        <v>595184</v>
       </c>
       <c r="R16" t="n">
-        <v>7097754</v>
+        <v>7097619</v>
       </c>
       <c r="S16" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,12 +2306,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2322,48 +2322,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937559</v>
+        <v>133937634</v>
       </c>
       <c r="B17" t="n">
-        <v>80368</v>
+        <v>83351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595116</v>
+        <v>595247</v>
       </c>
       <c r="R17" t="n">
-        <v>7097595</v>
+        <v>7097605</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,64 +2417,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937634</v>
+        <v>133937559</v>
       </c>
       <c r="B18" t="n">
-        <v>83344</v>
+        <v>80375</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595247</v>
+        <v>595116</v>
       </c>
       <c r="R18" t="n">
-        <v>7097605</v>
+        <v>7097595</v>
       </c>
       <c r="S18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,7 +2499,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2513,7 +2509,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,22 +2524,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>133937584</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>133937593</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,48 +2762,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937560</v>
+        <v>133937589</v>
       </c>
       <c r="B21" t="n">
-        <v>80474</v>
+        <v>80486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595193</v>
+        <v>595191</v>
       </c>
       <c r="R21" t="n">
-        <v>7097655</v>
+        <v>7097650</v>
       </c>
       <c r="S21" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,12 +2857,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2873,48 +2873,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937589</v>
+        <v>133937560</v>
       </c>
       <c r="B22" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595191</v>
+        <v>595193</v>
       </c>
       <c r="R22" t="n">
-        <v>7097650</v>
+        <v>7097655</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,12 +2968,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2987,7 +2987,7 @@
         <v>133937623</v>
       </c>
       <c r="B23" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>133937600</v>
       </c>
       <c r="B24" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3202,48 +3202,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133937629</v>
+        <v>133937591</v>
       </c>
       <c r="B25" t="n">
-        <v>96399</v>
+        <v>79366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595437</v>
+        <v>595199</v>
       </c>
       <c r="R25" t="n">
-        <v>7097860</v>
+        <v>7097678</v>
       </c>
       <c r="S25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3297,60 +3297,64 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133937591</v>
+        <v>133937629</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>96406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595199</v>
+        <v>595437</v>
       </c>
       <c r="R26" t="n">
-        <v>7097678</v>
+        <v>7097860</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3379,7 +3383,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3389,7 +3393,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,19 +3408,15 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3547,7 +3547,7 @@
         <v>133937567</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>133937566</v>
       </c>
       <c r="B29" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3762,34 +3762,30 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133937569</v>
+        <v>133937573</v>
       </c>
       <c r="B30" t="n">
-        <v>96399</v>
+        <v>91987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3797,13 +3793,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595355</v>
+        <v>595298</v>
       </c>
       <c r="R30" t="n">
-        <v>7097870</v>
+        <v>7097915</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3832,7 +3828,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3842,7 +3838,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,30 +3869,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937573</v>
+        <v>133937569</v>
       </c>
       <c r="B31" t="n">
-        <v>91980</v>
+        <v>96406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595298</v>
+        <v>595355</v>
       </c>
       <c r="R31" t="n">
-        <v>7097915</v>
+        <v>7097870</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,7 +3983,7 @@
         <v>133937592</v>
       </c>
       <c r="B32" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133937632</v>
+        <v>133937588</v>
       </c>
       <c r="B33" t="n">
-        <v>83336</v>
+        <v>80481</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,37 +4102,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595212</v>
+        <v>595190</v>
       </c>
       <c r="R33" t="n">
-        <v>7097665</v>
+        <v>7097648</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,22 +4186,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133937588</v>
+        <v>133937632</v>
       </c>
       <c r="B34" t="n">
-        <v>80474</v>
+        <v>83343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,37 +4213,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595190</v>
+        <v>595212</v>
       </c>
       <c r="R34" t="n">
-        <v>7097648</v>
+        <v>7097665</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4268,7 +4272,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4278,7 +4282,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4293,19 +4297,15 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4421,32 +4421,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133937595</v>
+        <v>133937597</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>96406</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595379</v>
+        <v>595445</v>
       </c>
       <c r="R36" t="n">
-        <v>7097727</v>
+        <v>7097853</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4532,32 +4532,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133937597</v>
+        <v>133937595</v>
       </c>
       <c r="B37" t="n">
-        <v>96399</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595445</v>
+        <v>595379</v>
       </c>
       <c r="R37" t="n">
-        <v>7097853</v>
+        <v>7097727</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4643,48 +4643,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133937590</v>
+        <v>133937621</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>80375</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595196</v>
+        <v>595159</v>
       </c>
       <c r="R38" t="n">
-        <v>7097666</v>
+        <v>7097615</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4738,64 +4738,68 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133937621</v>
+        <v>133937563</v>
       </c>
       <c r="B39" t="n">
-        <v>80368</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595159</v>
+        <v>595342</v>
       </c>
       <c r="R39" t="n">
-        <v>7097615</v>
+        <v>7097705</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4824,7 +4828,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4834,7 +4838,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4849,22 +4853,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133937563</v>
+        <v>133937590</v>
       </c>
       <c r="B40" t="n">
-        <v>57972</v>
+        <v>79366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4872,45 +4880,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595342</v>
+        <v>595196</v>
       </c>
       <c r="R40" t="n">
-        <v>7097705</v>
+        <v>7097666</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4964,12 +4964,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4983,7 +4983,7 @@
         <v>133937558</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>133937594</v>
       </c>
       <c r="B42" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>133937570</v>
       </c>
       <c r="B43" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>133937586</v>
       </c>
       <c r="B44" t="n">
-        <v>80368</v>
+        <v>80375</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>133965737</v>
       </c>
       <c r="B45" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>133965736</v>
       </c>
       <c r="B46" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>133965739</v>
       </c>
       <c r="B47" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133938031</v>
+        <v>133937600</v>
       </c>
       <c r="B2" t="n">
-        <v>80375</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595191</v>
+        <v>595222</v>
       </c>
       <c r="R2" t="n">
-        <v>7097636</v>
+        <v>7097669</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På Asp</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133937626</v>
+        <v>133937632</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595413</v>
+        <v>595212</v>
       </c>
       <c r="R3" t="n">
-        <v>7097755</v>
+        <v>7097665</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,48 +893,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133937631</v>
+        <v>133965739</v>
       </c>
       <c r="B4" t="n">
-        <v>96406</v>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>29 maj, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595307</v>
+        <v>595211</v>
       </c>
       <c r="R4" t="n">
-        <v>7097797</v>
+        <v>7097663</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,28 +985,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>David Häggblad, Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133937574</v>
+        <v>133937570</v>
       </c>
       <c r="B5" t="n">
-        <v>91963</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595390</v>
+        <v>595369</v>
       </c>
       <c r="R5" t="n">
-        <v>7097932</v>
+        <v>7097884</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133937572</v>
+        <v>133937574</v>
       </c>
       <c r="B6" t="n">
-        <v>91987</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,19 +1130,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595308</v>
+        <v>595390</v>
       </c>
       <c r="R6" t="n">
-        <v>7097929</v>
+        <v>7097932</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1182,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133937561</v>
+        <v>133937594</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,37 +1241,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595216</v>
+        <v>595325</v>
       </c>
       <c r="R7" t="n">
-        <v>7097632</v>
+        <v>7097704</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1334,32 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133937628</v>
+        <v>133937625</v>
       </c>
       <c r="B8" t="n">
-        <v>91930</v>
+        <v>91970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595416</v>
+        <v>595324</v>
       </c>
       <c r="R8" t="n">
-        <v>7097833</v>
+        <v>7097699</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,45 +1448,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133937630</v>
+        <v>133937569</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>96413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595406</v>
+        <v>595355</v>
       </c>
       <c r="R9" t="n">
-        <v>7097841</v>
+        <v>7097870</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1511,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1528,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,60 +1543,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133937633</v>
+        <v>133937575</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>96413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595242</v>
+        <v>595436</v>
       </c>
       <c r="R10" t="n">
-        <v>7097623</v>
+        <v>7097885</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1628,12 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>fertil</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,22 +1654,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133937575</v>
+        <v>133937597</v>
       </c>
       <c r="B11" t="n">
-        <v>96406</v>
+        <v>96413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,17 +1701,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595436</v>
+        <v>595445</v>
       </c>
       <c r="R11" t="n">
-        <v>7097885</v>
+        <v>7097853</v>
       </c>
       <c r="S11" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,12 +1765,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1774,7 +1784,7 @@
         <v>133937599</v>
       </c>
       <c r="B12" t="n">
-        <v>96406</v>
+        <v>96413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,48 +1892,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133937596</v>
+        <v>133937629</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>96413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595406</v>
+        <v>595437</v>
       </c>
       <c r="R13" t="n">
-        <v>7097778</v>
+        <v>7097860</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,48 +1987,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133937625</v>
+        <v>133937631</v>
       </c>
       <c r="B14" t="n">
-        <v>91963</v>
+        <v>96413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2028,10 +2034,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595324</v>
+        <v>595307</v>
       </c>
       <c r="R14" t="n">
-        <v>7097699</v>
+        <v>7097797</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,7 +2069,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2079,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,48 +2106,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133937564</v>
+        <v>133937628</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>91937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595317</v>
+        <v>595416</v>
       </c>
       <c r="R15" t="n">
-        <v>7097754</v>
+        <v>7097833</v>
       </c>
       <c r="S15" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2170,7 +2176,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,7 +2186,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,30 +2201,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133937585</v>
+        <v>133937558</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2242,17 +2244,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595184</v>
+        <v>595093</v>
       </c>
       <c r="R16" t="n">
-        <v>7097619</v>
+        <v>7097487</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,7 +2283,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2293,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,12 +2308,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2322,48 +2324,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133937634</v>
+        <v>133937564</v>
       </c>
       <c r="B17" t="n">
-        <v>83351</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595247</v>
+        <v>595317</v>
       </c>
       <c r="R17" t="n">
-        <v>7097605</v>
+        <v>7097754</v>
       </c>
       <c r="S17" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2394,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2404,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,44 +2419,48 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133937559</v>
+        <v>133937567</v>
       </c>
       <c r="B18" t="n">
-        <v>80375</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2464,13 +2470,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595116</v>
+        <v>595328</v>
       </c>
       <c r="R18" t="n">
-        <v>7097595</v>
+        <v>7097836</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,7 +2505,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2509,7 +2515,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2540,14 +2546,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133937584</v>
+        <v>133937576</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2569,19 +2575,22 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595175</v>
+        <v>595223</v>
       </c>
       <c r="R19" t="n">
-        <v>7097596</v>
+        <v>7097599</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,7 +2619,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2620,7 +2629,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,18 +2643,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2651,14 +2666,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133937593</v>
+        <v>133937583</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2686,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595311</v>
+        <v>595172</v>
       </c>
       <c r="R20" t="n">
-        <v>7097651</v>
+        <v>7097572</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2721,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2731,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,32 +2777,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133937589</v>
+        <v>133937584</v>
       </c>
       <c r="B21" t="n">
-        <v>80486</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2797,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595191</v>
+        <v>595175</v>
       </c>
       <c r="R21" t="n">
-        <v>7097650</v>
+        <v>7097596</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2832,7 +2847,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2842,7 +2857,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,48 +2888,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133937560</v>
+        <v>133937585</v>
       </c>
       <c r="B22" t="n">
-        <v>80481</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595193</v>
+        <v>595184</v>
       </c>
       <c r="R22" t="n">
-        <v>7097655</v>
+        <v>7097619</v>
       </c>
       <c r="S22" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2943,7 +2958,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2953,7 +2968,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,12 +2983,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2984,48 +2999,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133937623</v>
+        <v>133937590</v>
       </c>
       <c r="B23" t="n">
-        <v>99210</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595221</v>
+        <v>595196</v>
       </c>
       <c r="R23" t="n">
-        <v>7097668</v>
+        <v>7097666</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3054,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3064,7 +3079,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3079,44 +3094,48 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133937600</v>
+        <v>133937591</v>
       </c>
       <c r="B24" t="n">
-        <v>83343</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,13 +3145,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595222</v>
+        <v>595199</v>
       </c>
       <c r="R24" t="n">
-        <v>7097669</v>
+        <v>7097678</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,7 +3180,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3171,7 +3190,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3202,14 +3221,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133937591</v>
+        <v>133937592</v>
       </c>
       <c r="B25" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3237,13 +3256,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595199</v>
+        <v>595271</v>
       </c>
       <c r="R25" t="n">
-        <v>7097678</v>
+        <v>7097671</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,7 +3291,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3282,7 +3301,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3313,48 +3332,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133937629</v>
+        <v>133937593</v>
       </c>
       <c r="B26" t="n">
-        <v>96406</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595437</v>
+        <v>595311</v>
       </c>
       <c r="R26" t="n">
-        <v>7097860</v>
+        <v>7097651</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3383,7 +3402,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3393,7 +3412,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3408,68 +3427,64 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133937571</v>
+        <v>133937595</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595321</v>
+        <v>595379</v>
       </c>
       <c r="R27" t="n">
-        <v>7097929</v>
+        <v>7097727</v>
       </c>
       <c r="S27" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3498,7 +3513,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3508,19 +3523,14 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3528,12 +3538,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3544,14 +3554,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133937567</v>
+        <v>133937596</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3575,17 +3585,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595328</v>
+        <v>595406</v>
       </c>
       <c r="R28" t="n">
-        <v>7097836</v>
+        <v>7097778</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3614,7 +3624,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3624,7 +3634,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3639,12 +3649,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3655,44 +3665,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133937566</v>
+        <v>133937620</v>
       </c>
       <c r="B29" t="n">
-        <v>91987</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595306</v>
+        <v>595169</v>
       </c>
       <c r="R29" t="n">
-        <v>7097799</v>
+        <v>7097572</v>
       </c>
       <c r="S29" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3721,7 +3735,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3731,7 +3745,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,60 +3760,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133937573</v>
+        <v>133937630</v>
       </c>
       <c r="B30" t="n">
-        <v>91987</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595298</v>
+        <v>595406</v>
       </c>
       <c r="R30" t="n">
-        <v>7097915</v>
+        <v>7097841</v>
       </c>
       <c r="S30" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3828,7 +3842,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3838,7 +3852,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,64 +3867,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133937569</v>
+        <v>133937633</v>
       </c>
       <c r="B31" t="n">
-        <v>96406</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595355</v>
+        <v>595242</v>
       </c>
       <c r="R31" t="n">
-        <v>7097870</v>
+        <v>7097623</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3939,7 +3949,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3949,7 +3959,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3964,30 +3979,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133937592</v>
+        <v>133965736</v>
       </c>
       <c r="B32" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4009,19 +4020,22 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>29 maj, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595271</v>
+        <v>595176</v>
       </c>
       <c r="R32" t="n">
-        <v>7097671</v>
+        <v>7097609</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4050,7 +4064,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4060,7 +4074,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4069,18 +4083,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>David Häggblad, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4091,10 +4106,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133937588</v>
+        <v>133937634</v>
       </c>
       <c r="B33" t="n">
-        <v>80481</v>
+        <v>83358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,37 +4117,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595190</v>
+        <v>595247</v>
       </c>
       <c r="R33" t="n">
-        <v>7097648</v>
+        <v>7097605</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4161,7 +4176,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4171,7 +4186,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4186,64 +4201,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133937632</v>
+        <v>133937559</v>
       </c>
       <c r="B34" t="n">
-        <v>83343</v>
+        <v>80382</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595212</v>
+        <v>595116</v>
       </c>
       <c r="R34" t="n">
-        <v>7097665</v>
+        <v>7097595</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4272,7 +4283,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4282,7 +4293,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4297,22 +4308,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133937627</v>
+        <v>133937586</v>
       </c>
       <c r="B35" t="n">
-        <v>57162</v>
+        <v>80382</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,34 +4335,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595418</v>
+        <v>595185</v>
       </c>
       <c r="R35" t="n">
-        <v>7097757</v>
+        <v>7097623</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4379,7 +4394,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4389,12 +4404,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4409,22 +4419,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Anton Brall</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133937597</v>
+        <v>133937621</v>
       </c>
       <c r="B36" t="n">
-        <v>96406</v>
+        <v>80382</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4432,34 +4446,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595445</v>
+        <v>595159</v>
       </c>
       <c r="R36" t="n">
-        <v>7097853</v>
+        <v>7097615</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4491,7 +4505,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4501,7 +4515,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4516,61 +4530,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133937595</v>
+        <v>133938031</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>80382</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595379</v>
+        <v>595191</v>
       </c>
       <c r="R37" t="n">
-        <v>7097727</v>
+        <v>7097636</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4602,7 +4612,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4612,7 +4622,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På Asp</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4627,12 +4642,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4643,48 +4658,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133937621</v>
+        <v>133937560</v>
       </c>
       <c r="B38" t="n">
-        <v>80375</v>
+        <v>80488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595159</v>
+        <v>595193</v>
       </c>
       <c r="R38" t="n">
-        <v>7097615</v>
+        <v>7097655</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4713,7 +4728,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4723,7 +4738,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4738,22 +4753,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133937563</v>
+        <v>133937588</v>
       </c>
       <c r="B39" t="n">
-        <v>57972</v>
+        <v>80488</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,45 +4780,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595342</v>
+        <v>595190</v>
       </c>
       <c r="R39" t="n">
-        <v>7097705</v>
+        <v>7097648</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4828,7 +4839,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4838,7 +4849,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4853,12 +4864,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4869,10 +4880,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133937590</v>
+        <v>133965737</v>
       </c>
       <c r="B40" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4880,37 +4891,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>29 maj, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595196</v>
+        <v>595190</v>
       </c>
       <c r="R40" t="n">
-        <v>7097666</v>
+        <v>7097640</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4939,7 +4953,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4949,7 +4963,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4958,18 +4972,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>David Häggblad, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4980,48 +4995,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133937558</v>
+        <v>133937589</v>
       </c>
       <c r="B41" t="n">
-        <v>79366</v>
+        <v>80493</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grabboksjön, Ås lm</t>
+          <t>a 54317-2025, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595093</v>
+        <v>595191</v>
       </c>
       <c r="R41" t="n">
-        <v>7097487</v>
+        <v>7097650</v>
       </c>
       <c r="S41" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5050,7 +5065,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5060,7 +5075,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5075,12 +5090,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Brall</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5091,48 +5106,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133937594</v>
+        <v>133937561</v>
       </c>
       <c r="B42" t="n">
-        <v>91963</v>
+        <v>57972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595325</v>
+        <v>595216</v>
       </c>
       <c r="R42" t="n">
-        <v>7097704</v>
+        <v>7097632</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5161,7 +5176,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5171,7 +5186,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,12 +5201,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5202,48 +5217,56 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133937570</v>
+        <v>133937563</v>
       </c>
       <c r="B43" t="n">
-        <v>91963</v>
+        <v>57972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595369</v>
+        <v>595342</v>
       </c>
       <c r="R43" t="n">
-        <v>7097884</v>
+        <v>7097705</v>
       </c>
       <c r="S43" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5272,7 +5295,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5282,7 +5305,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5313,10 +5336,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133937586</v>
+        <v>133937626</v>
       </c>
       <c r="B44" t="n">
-        <v>80375</v>
+        <v>57972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5324,34 +5347,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>a 54317-2025, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595185</v>
+        <v>595413</v>
       </c>
       <c r="R44" t="n">
-        <v>7097623</v>
+        <v>7097755</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5383,7 +5406,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5393,7 +5416,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5408,26 +5431,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anton Brall</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133965737</v>
+        <v>133937571</v>
       </c>
       <c r="B45" t="n">
-        <v>80481</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5435,40 +5454,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>29 maj, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595190</v>
+        <v>595321</v>
       </c>
       <c r="R45" t="n">
-        <v>7097640</v>
+        <v>7097929</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5497,7 +5521,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5507,28 +5531,32 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>David Häggblad, Karin Häggblad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5539,48 +5567,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133965736</v>
+        <v>133937627</v>
       </c>
       <c r="B46" t="n">
-        <v>79366</v>
+        <v>57162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>29 maj, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595176</v>
+        <v>595418</v>
       </c>
       <c r="R46" t="n">
-        <v>7097609</v>
+        <v>7097757</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5612,7 +5637,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5622,7 +5647,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5631,74 +5661,66 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>David Häggblad, Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133965739</v>
+        <v>133937623</v>
       </c>
       <c r="B47" t="n">
-        <v>83343</v>
+        <v>99217</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>29 maj, Ås lm</t>
+          <t>Grabboksjön, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595211</v>
+        <v>595221</v>
       </c>
       <c r="R47" t="n">
-        <v>7097663</v>
+        <v>7097668</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5727,7 +5749,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5737,7 +5759,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5746,26 +5768,21 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>David Häggblad, Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Inventeringshelg Åsele maj 2026</t>
-        </is>
-      </c>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54317-2025 artfynd.xlsx
+++ b/artfynd/A 54317-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937632</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965739</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937570</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937574</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937594</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937625</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937569</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937575</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937597</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937599</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,6 +2056,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937629</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2103,6 +2168,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937631</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2210,6 +2280,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937628</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2321,6 +2396,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937558</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937564</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2541,6 +2626,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937567</t>
         </is>
       </c>
     </row>
@@ -2663,6 +2753,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937576</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2774,6 +2869,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937583</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2885,6 +2985,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937584</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2996,6 +3101,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937585</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3107,6 +3217,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937590</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3218,6 +3333,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937591</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3329,6 +3449,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937592</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3440,6 +3565,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937593</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3551,6 +3681,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937595</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3662,6 +3797,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937596</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3769,6 +3909,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937620</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3876,6 +4021,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937630</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3988,6 +4138,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937633</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4103,6 +4258,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965736</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4210,6 +4370,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937634</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4321,6 +4486,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937559</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4432,6 +4602,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937586</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4539,6 +4714,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937621</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4655,6 +4835,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133938031</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4766,6 +4951,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937560</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4875,6 +5065,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937588</t>
         </is>
       </c>
     </row>
@@ -4992,6 +5187,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965737</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5103,6 +5303,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937589</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5214,6 +5419,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937561</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5333,6 +5543,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937563</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5440,6 +5655,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937626</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5564,6 +5784,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937571</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5676,6 +5901,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937627</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5783,8 +6013,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133937623</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>